--- a/duoki_editor/resources/data/blank/海洋-魔法师-3-blank.xlsx
+++ b/duoki_editor/resources/data/blank/海洋-魔法师-3-blank.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="31">
   <si>
     <t>stage_id</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t>寻找东西任务_第4次</t>
+  </si>
+  <si>
+    <t>寻找东西任务_帮助</t>
   </si>
   <si>
     <t>(生成图片_提示词)</t>
@@ -493,10 +496,10 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -510,10 +513,10 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -527,10 +530,10 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -544,10 +547,10 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -561,10 +564,10 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -578,10 +581,10 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -592,13 +595,13 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -609,10 +612,10 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9">
         <v>200617</v>
@@ -626,13 +629,13 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -643,13 +646,13 @@
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
